--- a/Scripts_Data/Data_Vehicle/sm_car_ARTTU_Powertrain.xlsx
+++ b/Scripts_Data/Data_Vehicle/sm_car_ARTTU_Powertrain.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Desktop/FSAE/Vehicle Model/Main/Develop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Desktop/FSAE/Vehicle Model/VehicleModel/Scripts_Data/Data_Vehicle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065EC984-1FBA-EB40-8CC0-62199660AD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280B0E4C-C3FC-2A42-B007-E177DA193841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12340" yWindow="720" windowWidth="17160" windowHeight="19820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7040" yWindow="720" windowWidth="17160" windowHeight="19820" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power" sheetId="5" r:id="rId1"/>
@@ -314,13 +314,13 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="8"/>
+      <sz val="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
@@ -1101,9 +1101,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1131,6 +1128,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3001,7 +3001,7 @@
       <c r="E9" s="29"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3660,7 +3660,7 @@
       <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="87" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="11"/>
@@ -3673,7 +3673,7 @@
       <c r="E5" s="13"/>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="88" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="14"/>
@@ -3686,7 +3686,7 @@
       <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="88" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="14"/>
@@ -3699,7 +3699,7 @@
       <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="89" t="s">
+      <c r="A8" s="88" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="14"/>
@@ -3712,7 +3712,7 @@
       <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="89" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="18"/>
@@ -3790,7 +3790,7 @@
       <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="90" t="s">
         <v>32</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -3807,7 +3807,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="92"/>
+      <c r="A6" s="91"/>
       <c r="B6" s="14" t="s">
         <v>35</v>
       </c>
@@ -3822,7 +3822,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="93"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="14" t="s">
         <v>39</v>
       </c>
@@ -3837,7 +3837,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="90" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -3854,7 +3854,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="92"/>
+      <c r="A9" s="91"/>
       <c r="B9" s="14" t="s">
         <v>35</v>
       </c>
@@ -3869,7 +3869,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="93"/>
+      <c r="A10" s="92"/>
       <c r="B10" s="14" t="s">
         <v>44</v>
       </c>
@@ -3884,29 +3884,29 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="91" t="s">
+      <c r="A11" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="85" t="s">
         <v>35</v>
       </c>
       <c r="C11" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="85" t="s">
+      <c r="D11" s="84" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="64"/>
     </row>
     <row r="12" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="92"/>
-      <c r="B12" s="86" t="s">
+      <c r="A12" s="91"/>
+      <c r="B12" s="85" t="s">
         <v>47</v>
       </c>
       <c r="C12" s="59">
         <v>24</v>
       </c>
-      <c r="D12" s="85" t="s">
+      <c r="D12" s="84" t="s">
         <v>48</v>
       </c>
       <c r="E12" s="64"/>
@@ -3915,9 +3915,9 @@
       <c r="A13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="87"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="59">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>50</v>
@@ -3940,130 +3940,129 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF150FC-6821-5C41-A667-322EB01AF871}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A1" s="84">
+    <row r="1" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="94">
         <v>195.6</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="94">
+        <v>193.7</v>
+      </c>
+      <c r="C1" s="94">
+        <v>192.4</v>
+      </c>
+      <c r="D1" s="94">
+        <v>191.1</v>
+      </c>
+      <c r="E1" s="94">
+        <v>190.8</v>
+      </c>
+      <c r="F1" s="94">
+        <v>189.1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="94">
+        <v>187</v>
+      </c>
+      <c r="B2" s="94">
+        <v>186.4</v>
+      </c>
+      <c r="C2" s="94">
+        <v>185.2</v>
+      </c>
+      <c r="D2" s="94">
+        <v>184.8</v>
+      </c>
+      <c r="E2" s="94">
+        <v>182.4</v>
+      </c>
+      <c r="F2" s="94">
         <v>180.9</v>
       </c>
-      <c r="C1">
+    </row>
+    <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="94">
         <v>179.5</v>
       </c>
-      <c r="D1">
+      <c r="B3" s="94">
+        <v>178.2</v>
+      </c>
+      <c r="C3" s="94">
+        <v>177.9</v>
+      </c>
+      <c r="D3" s="94">
+        <v>176.7</v>
+      </c>
+      <c r="E3" s="94">
+        <v>174.9</v>
+      </c>
+      <c r="F3" s="94">
+        <v>171.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="94">
         <v>169.8</v>
       </c>
-      <c r="E1">
+      <c r="B4" s="94">
+        <v>168.7</v>
+      </c>
+      <c r="C4" s="94">
+        <v>166.5</v>
+      </c>
+      <c r="D4" s="94">
+        <v>164.7</v>
+      </c>
+      <c r="E4" s="94">
+        <v>161.9</v>
+      </c>
+      <c r="F4" s="94">
+        <v>161.19999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A5" s="94">
         <v>160.69999999999999</v>
       </c>
-      <c r="F1">
+      <c r="B5" s="94">
+        <v>159.4</v>
+      </c>
+      <c r="C5" s="94">
+        <v>158.6</v>
+      </c>
+      <c r="D5" s="94">
+        <v>157.5</v>
+      </c>
+      <c r="E5" s="94">
+        <v>156.9</v>
+      </c>
+      <c r="F5" s="94">
+        <v>155.19999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A6" s="94">
         <v>154.80000000000001</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2">
-        <v>193.7</v>
-      </c>
-      <c r="B2">
-        <v>182.4</v>
-      </c>
-      <c r="C2">
-        <v>178.2</v>
-      </c>
-      <c r="D2">
-        <v>168.7</v>
-      </c>
-      <c r="E2">
-        <v>159.4</v>
-      </c>
-      <c r="F2">
+      <c r="B6" s="94">
         <v>153.69999999999999</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3">
-        <v>192.4</v>
-      </c>
-      <c r="B3">
-        <v>184.8</v>
-      </c>
-      <c r="C3">
-        <v>177.9</v>
-      </c>
-      <c r="D3">
-        <v>166.5</v>
-      </c>
-      <c r="E3">
-        <v>158.6</v>
-      </c>
-      <c r="F3">
+      <c r="C6" s="94">
         <v>152.4</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>191.1</v>
-      </c>
-      <c r="B4">
-        <v>185.2</v>
-      </c>
-      <c r="C4">
-        <v>176.7</v>
-      </c>
-      <c r="D4">
-        <v>164.7</v>
-      </c>
-      <c r="E4">
-        <v>157.5</v>
-      </c>
-      <c r="F4">
+      <c r="D6" s="94">
         <v>151.69999999999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>190.8</v>
-      </c>
-      <c r="B5">
-        <v>186.4</v>
-      </c>
-      <c r="C5">
-        <v>174.9</v>
-      </c>
-      <c r="D5">
-        <v>161.9</v>
-      </c>
-      <c r="E5">
-        <v>156.9</v>
-      </c>
-      <c r="F5">
+      <c r="E6" s="94">
         <v>150.30000000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A6">
-        <v>189.1</v>
-      </c>
-      <c r="B6">
-        <v>187</v>
-      </c>
-      <c r="C6">
-        <v>171.2</v>
-      </c>
-      <c r="D6">
-        <v>161.19999999999999</v>
-      </c>
-      <c r="E6">
-        <v>155.19999999999999</v>
-      </c>
-      <c r="F6">
+      <c r="F6" s="94">
         <v>148.80000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4075,122 +4074,122 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A1">
+      <c r="A1" s="94">
         <v>4.2300000000000003E-3</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="94">
+        <v>3.8E-3</v>
+      </c>
+      <c r="C1" s="94">
+        <v>3.7699999999999999E-3</v>
+      </c>
+      <c r="D1" s="94">
+        <v>3.6600000000000001E-3</v>
+      </c>
+      <c r="E1" s="94">
+        <v>3.62E-3</v>
+      </c>
+      <c r="F1" s="94">
+        <v>3.5899999999999999E-3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="94">
         <v>3.5699999999999998E-3</v>
       </c>
-      <c r="C1">
+      <c r="B2" s="94">
+        <v>3.2699999999999999E-3</v>
+      </c>
+      <c r="C2" s="94">
+        <v>3.1900000000000001E-3</v>
+      </c>
+      <c r="D2" s="94">
+        <v>3.8E-3</v>
+      </c>
+      <c r="E2" s="94">
+        <v>3.13E-3</v>
+      </c>
+      <c r="F2" s="94">
+        <v>3.0799999999999998E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="94">
         <v>3.15E-3</v>
       </c>
-      <c r="D1">
+      <c r="B3" s="94">
+        <v>2.98E-3</v>
+      </c>
+      <c r="C3" s="94">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="D3" s="94">
+        <v>2.8E-3</v>
+      </c>
+      <c r="E3" s="94">
         <v>2.7699999999999999E-3</v>
       </c>
-      <c r="E1">
-        <v>3.3300000000000001E-3</v>
-      </c>
-      <c r="F1">
+      <c r="F3" s="94">
+        <v>2.7499999999999998E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="94">
+        <v>2.7699999999999999E-3</v>
+      </c>
+      <c r="B4" s="94">
+        <v>2.8800000000000002E-3</v>
+      </c>
+      <c r="C4" s="94">
+        <v>3.1099999999999999E-3</v>
+      </c>
+      <c r="D4" s="94">
+        <v>3.2399999999999998E-3</v>
+      </c>
+      <c r="E4" s="94">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="F4" s="94">
+        <v>2.7299999999999998E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="94">
+        <v>3.3E-3</v>
+      </c>
+      <c r="B5" s="94">
+        <v>2.8900000000000002E-3</v>
+      </c>
+      <c r="C5" s="94">
         <v>2.9399999999999999E-3</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2">
-        <v>3.8E-3</v>
-      </c>
-      <c r="B2">
-        <v>3.2699999999999999E-3</v>
-      </c>
-      <c r="C2">
-        <v>2.98E-3</v>
-      </c>
-      <c r="D2">
+      <c r="D5" s="94">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E5" s="94">
+        <v>2.9299999999999999E-3</v>
+      </c>
+      <c r="F5" s="94">
         <v>2.8800000000000002E-3</v>
       </c>
-      <c r="E2">
-        <v>2.8900000000000002E-3</v>
-      </c>
-      <c r="F2">
+    </row>
+    <row r="6" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="94">
+        <v>2.9399999999999999E-3</v>
+      </c>
+      <c r="B6" s="94">
         <v>3.29E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3">
-        <v>3.7699999999999999E-3</v>
-      </c>
-      <c r="B3">
-        <v>3.1900000000000001E-3</v>
-      </c>
-      <c r="C3">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="D3">
-        <v>3.1099999999999999E-3</v>
-      </c>
-      <c r="E3">
-        <v>2.9399999999999999E-3</v>
-      </c>
-      <c r="F3">
+      <c r="C6" s="94">
         <v>3.1199999999999999E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4">
-        <v>3.6600000000000001E-3</v>
-      </c>
-      <c r="B4">
-        <v>3.8E-3</v>
-      </c>
-      <c r="C4">
-        <v>2.8E-3</v>
-      </c>
-      <c r="D4">
-        <v>3.2399999999999998E-3</v>
-      </c>
-      <c r="E4">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="F4">
+      <c r="D6" s="94">
         <v>2.7299999999999998E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5">
-        <v>3.62E-3</v>
-      </c>
-      <c r="B5">
-        <v>3.13E-3</v>
-      </c>
-      <c r="C5">
-        <v>2.7699999999999999E-3</v>
-      </c>
-      <c r="D5">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="E5">
-        <v>2.9299999999999999E-3</v>
-      </c>
-      <c r="F5">
+      <c r="E6" s="94">
         <v>2.5999999999999999E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6">
-        <v>3.5899999999999999E-3</v>
-      </c>
-      <c r="B6">
-        <v>3.0799999999999998E-3</v>
-      </c>
-      <c r="C6">
-        <v>2.7499999999999998E-3</v>
-      </c>
-      <c r="D6">
-        <v>2.7299999999999998E-3</v>
-      </c>
-      <c r="E6">
-        <v>2.8800000000000002E-3</v>
-      </c>
-      <c r="F6">
+      <c r="F6" s="94">
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
@@ -4256,7 +4255,7 @@
       <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="90" t="s">
         <v>51</v>
       </c>
       <c r="B5" s="47" t="s">
@@ -4271,7 +4270,7 @@
       <c r="E5" s="22"/>
     </row>
     <row r="6" spans="1:5" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="94"/>
+      <c r="A6" s="93"/>
       <c r="B6" s="48" t="s">
         <v>55</v>
       </c>
@@ -4297,7 +4296,7 @@
       <c r="E7" s="81"/>
     </row>
     <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="90" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="49" t="s">
@@ -4312,7 +4311,7 @@
       <c r="E8" s="45"/>
     </row>
     <row r="9" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="92"/>
+      <c r="A9" s="91"/>
       <c r="B9" s="50" t="s">
         <v>55</v>
       </c>
@@ -4325,7 +4324,7 @@
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="94"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="61" t="s">
         <v>28</v>
       </c>
@@ -4338,7 +4337,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="91" t="s">
+      <c r="A11" s="90" t="s">
         <v>60</v>
       </c>
       <c r="B11" s="65" t="s">
@@ -4353,7 +4352,7 @@
       <c r="E11" s="68"/>
     </row>
     <row r="12" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="92"/>
+      <c r="A12" s="91"/>
       <c r="B12" s="69" t="s">
         <v>63</v>
       </c>
@@ -4366,7 +4365,7 @@
       <c r="E12" s="72"/>
     </row>
     <row r="13" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="92"/>
+      <c r="A13" s="91"/>
       <c r="B13" s="69" t="s">
         <v>28</v>
       </c>
@@ -4379,7 +4378,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="92"/>
+      <c r="A14" s="91"/>
       <c r="B14" s="69" t="s">
         <v>64</v>
       </c>
@@ -4392,7 +4391,7 @@
       <c r="E14" s="72"/>
     </row>
     <row r="15" spans="1:5" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="94"/>
+      <c r="A15" s="93"/>
       <c r="B15" s="73" t="s">
         <v>66</v>
       </c>
@@ -5388,26 +5387,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9557458c-24b5-4c97-84ed-4c402655f54f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="72e3c584-9879-4b35-b9d8-6a248c93e240" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009342B7EAA7728A4FA80A5CCAFE8D7EAF" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d037a5681ee6af0e7b5b5d0a2f99b20">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9557458c-24b5-4c97-84ed-4c402655f54f" xmlns:ns3="72e3c584-9879-4b35-b9d8-6a248c93e240" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="966978c8b125399653e7c255ac8e342d" ns2:_="" ns3:_="">
     <xsd:import namespace="9557458c-24b5-4c97-84ed-4c402655f54f"/>
@@ -5668,26 +5647,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3314153-DE99-46E1-9177-E565F1EC3082}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9557458c-24b5-4c97-84ed-4c402655f54f"/>
-    <ds:schemaRef ds:uri="72e3c584-9879-4b35-b9d8-6a248c93e240"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9557458c-24b5-4c97-84ed-4c402655f54f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="72e3c584-9879-4b35-b9d8-6a248c93e240" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192A017-E4B6-4D7F-8544-3BE30BB952E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A290CD9-4138-4944-8A1F-A307385BF4B2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5704,4 +5684,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3314153-DE99-46E1-9177-E565F1EC3082}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9557458c-24b5-4c97-84ed-4c402655f54f"/>
+    <ds:schemaRef ds:uri="72e3c584-9879-4b35-b9d8-6a248c93e240"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192A017-E4B6-4D7F-8544-3BE30BB952E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Scripts_Data/Data_Vehicle/sm_car_ARTTU_Powertrain.xlsx
+++ b/Scripts_Data/Data_Vehicle/sm_car_ARTTU_Powertrain.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Desktop/FSAE/Vehicle Model/VehicleModel/Scripts_Data/Data_Vehicle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280B0E4C-C3FC-2A42-B007-E177DA193841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2458B5-5250-044B-A5D4-803D0CC25C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7040" yWindow="720" windowWidth="17160" windowHeight="19820" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7040" yWindow="720" windowWidth="17160" windowHeight="19820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power" sheetId="5" r:id="rId1"/>
@@ -1117,6 +1117,9 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1128,9 +1131,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3790,7 +3790,7 @@
       <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="91" t="s">
         <v>32</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -3807,7 +3807,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="91"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="14" t="s">
         <v>35</v>
       </c>
@@ -3822,7 +3822,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="92"/>
+      <c r="A7" s="93"/>
       <c r="B7" s="14" t="s">
         <v>39</v>
       </c>
@@ -3837,7 +3837,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="90" t="s">
+      <c r="A8" s="91" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -3854,7 +3854,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="91"/>
+      <c r="A9" s="92"/>
       <c r="B9" s="14" t="s">
         <v>35</v>
       </c>
@@ -3869,7 +3869,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="92"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="14" t="s">
         <v>44</v>
       </c>
@@ -3884,7 +3884,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="91" t="s">
         <v>46</v>
       </c>
       <c r="B11" s="85" t="s">
@@ -3899,7 +3899,7 @@
       <c r="E11" s="64"/>
     </row>
     <row r="12" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="91"/>
+      <c r="A12" s="92"/>
       <c r="B12" s="85" t="s">
         <v>47</v>
       </c>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="B13" s="86"/>
       <c r="C13" s="59">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>50</v>
@@ -3944,122 +3944,122 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="94">
+      <c r="A1" s="90">
         <v>195.6</v>
       </c>
-      <c r="B1" s="94">
+      <c r="B1" s="90">
         <v>193.7</v>
       </c>
-      <c r="C1" s="94">
+      <c r="C1" s="90">
         <v>192.4</v>
       </c>
-      <c r="D1" s="94">
+      <c r="D1" s="90">
         <v>191.1</v>
       </c>
-      <c r="E1" s="94">
+      <c r="E1" s="90">
         <v>190.8</v>
       </c>
-      <c r="F1" s="94">
+      <c r="F1" s="90">
         <v>189.1</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="94">
+      <c r="A2" s="90">
         <v>187</v>
       </c>
-      <c r="B2" s="94">
+      <c r="B2" s="90">
         <v>186.4</v>
       </c>
-      <c r="C2" s="94">
+      <c r="C2" s="90">
         <v>185.2</v>
       </c>
-      <c r="D2" s="94">
+      <c r="D2" s="90">
         <v>184.8</v>
       </c>
-      <c r="E2" s="94">
+      <c r="E2" s="90">
         <v>182.4</v>
       </c>
-      <c r="F2" s="94">
+      <c r="F2" s="90">
         <v>180.9</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="94">
+      <c r="A3" s="90">
         <v>179.5</v>
       </c>
-      <c r="B3" s="94">
+      <c r="B3" s="90">
         <v>178.2</v>
       </c>
-      <c r="C3" s="94">
+      <c r="C3" s="90">
         <v>177.9</v>
       </c>
-      <c r="D3" s="94">
+      <c r="D3" s="90">
         <v>176.7</v>
       </c>
-      <c r="E3" s="94">
+      <c r="E3" s="90">
         <v>174.9</v>
       </c>
-      <c r="F3" s="94">
+      <c r="F3" s="90">
         <v>171.2</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="94">
+      <c r="A4" s="90">
         <v>169.8</v>
       </c>
-      <c r="B4" s="94">
+      <c r="B4" s="90">
         <v>168.7</v>
       </c>
-      <c r="C4" s="94">
+      <c r="C4" s="90">
         <v>166.5</v>
       </c>
-      <c r="D4" s="94">
+      <c r="D4" s="90">
         <v>164.7</v>
       </c>
-      <c r="E4" s="94">
+      <c r="E4" s="90">
         <v>161.9</v>
       </c>
-      <c r="F4" s="94">
+      <c r="F4" s="90">
         <v>161.19999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A5" s="94">
+      <c r="A5" s="90">
         <v>160.69999999999999</v>
       </c>
-      <c r="B5" s="94">
+      <c r="B5" s="90">
         <v>159.4</v>
       </c>
-      <c r="C5" s="94">
+      <c r="C5" s="90">
         <v>158.6</v>
       </c>
-      <c r="D5" s="94">
+      <c r="D5" s="90">
         <v>157.5</v>
       </c>
-      <c r="E5" s="94">
+      <c r="E5" s="90">
         <v>156.9</v>
       </c>
-      <c r="F5" s="94">
+      <c r="F5" s="90">
         <v>155.19999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A6" s="94">
+      <c r="A6" s="90">
         <v>154.80000000000001</v>
       </c>
-      <c r="B6" s="94">
+      <c r="B6" s="90">
         <v>153.69999999999999</v>
       </c>
-      <c r="C6" s="94">
+      <c r="C6" s="90">
         <v>152.4</v>
       </c>
-      <c r="D6" s="94">
+      <c r="D6" s="90">
         <v>151.69999999999999</v>
       </c>
-      <c r="E6" s="94">
+      <c r="E6" s="90">
         <v>150.30000000000001</v>
       </c>
-      <c r="F6" s="94">
+      <c r="F6" s="90">
         <v>148.80000000000001</v>
       </c>
     </row>
@@ -4074,122 +4074,122 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="A1" s="94">
+      <c r="A1" s="90">
         <v>4.2300000000000003E-3</v>
       </c>
-      <c r="B1" s="94">
+      <c r="B1" s="90">
         <v>3.8E-3</v>
       </c>
-      <c r="C1" s="94">
+      <c r="C1" s="90">
         <v>3.7699999999999999E-3</v>
       </c>
-      <c r="D1" s="94">
+      <c r="D1" s="90">
         <v>3.6600000000000001E-3</v>
       </c>
-      <c r="E1" s="94">
+      <c r="E1" s="90">
         <v>3.62E-3</v>
       </c>
-      <c r="F1" s="94">
+      <c r="F1" s="90">
         <v>3.5899999999999999E-3</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="94">
+      <c r="A2" s="90">
         <v>3.5699999999999998E-3</v>
       </c>
-      <c r="B2" s="94">
+      <c r="B2" s="90">
         <v>3.2699999999999999E-3</v>
       </c>
-      <c r="C2" s="94">
+      <c r="C2" s="90">
         <v>3.1900000000000001E-3</v>
       </c>
-      <c r="D2" s="94">
+      <c r="D2" s="90">
         <v>3.8E-3</v>
       </c>
-      <c r="E2" s="94">
+      <c r="E2" s="90">
         <v>3.13E-3</v>
       </c>
-      <c r="F2" s="94">
+      <c r="F2" s="90">
         <v>3.0799999999999998E-3</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="94">
+      <c r="A3" s="90">
         <v>3.15E-3</v>
       </c>
-      <c r="B3" s="94">
+      <c r="B3" s="90">
         <v>2.98E-3</v>
       </c>
-      <c r="C3" s="94">
+      <c r="C3" s="90">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="D3" s="94">
+      <c r="D3" s="90">
         <v>2.8E-3</v>
       </c>
-      <c r="E3" s="94">
+      <c r="E3" s="90">
         <v>2.7699999999999999E-3</v>
       </c>
-      <c r="F3" s="94">
+      <c r="F3" s="90">
         <v>2.7499999999999998E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="94">
+      <c r="A4" s="90">
         <v>2.7699999999999999E-3</v>
       </c>
-      <c r="B4" s="94">
+      <c r="B4" s="90">
         <v>2.8800000000000002E-3</v>
       </c>
-      <c r="C4" s="94">
+      <c r="C4" s="90">
         <v>3.1099999999999999E-3</v>
       </c>
-      <c r="D4" s="94">
+      <c r="D4" s="90">
         <v>3.2399999999999998E-3</v>
       </c>
-      <c r="E4" s="94">
+      <c r="E4" s="90">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="F4" s="94">
+      <c r="F4" s="90">
         <v>2.7299999999999998E-3</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="94">
+      <c r="A5" s="90">
         <v>3.3E-3</v>
       </c>
-      <c r="B5" s="94">
+      <c r="B5" s="90">
         <v>2.8900000000000002E-3</v>
       </c>
-      <c r="C5" s="94">
+      <c r="C5" s="90">
         <v>2.9399999999999999E-3</v>
       </c>
-      <c r="D5" s="94">
+      <c r="D5" s="90">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="E5" s="94">
+      <c r="E5" s="90">
         <v>2.9299999999999999E-3</v>
       </c>
-      <c r="F5" s="94">
+      <c r="F5" s="90">
         <v>2.8800000000000002E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="94">
+      <c r="A6" s="90">
         <v>2.9399999999999999E-3</v>
       </c>
-      <c r="B6" s="94">
+      <c r="B6" s="90">
         <v>3.29E-3</v>
       </c>
-      <c r="C6" s="94">
+      <c r="C6" s="90">
         <v>3.1199999999999999E-3</v>
       </c>
-      <c r="D6" s="94">
+      <c r="D6" s="90">
         <v>2.7299999999999998E-3</v>
       </c>
-      <c r="E6" s="94">
+      <c r="E6" s="90">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="F6" s="94">
+      <c r="F6" s="90">
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="90" t="s">
+      <c r="A5" s="91" t="s">
         <v>51</v>
       </c>
       <c r="B5" s="47" t="s">
@@ -4270,7 +4270,7 @@
       <c r="E5" s="22"/>
     </row>
     <row r="6" spans="1:5" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="93"/>
+      <c r="A6" s="94"/>
       <c r="B6" s="48" t="s">
         <v>55</v>
       </c>
@@ -4296,7 +4296,7 @@
       <c r="E7" s="81"/>
     </row>
     <row r="8" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="90" t="s">
+      <c r="A8" s="91" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="49" t="s">
@@ -4311,7 +4311,7 @@
       <c r="E8" s="45"/>
     </row>
     <row r="9" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="91"/>
+      <c r="A9" s="92"/>
       <c r="B9" s="50" t="s">
         <v>55</v>
       </c>
@@ -4324,7 +4324,7 @@
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="93"/>
+      <c r="A10" s="94"/>
       <c r="B10" s="61" t="s">
         <v>28</v>
       </c>
@@ -4337,7 +4337,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B11" s="65" t="s">
@@ -4352,7 +4352,7 @@
       <c r="E11" s="68"/>
     </row>
     <row r="12" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="91"/>
+      <c r="A12" s="92"/>
       <c r="B12" s="69" t="s">
         <v>63</v>
       </c>
@@ -4365,7 +4365,7 @@
       <c r="E12" s="72"/>
     </row>
     <row r="13" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="91"/>
+      <c r="A13" s="92"/>
       <c r="B13" s="69" t="s">
         <v>28</v>
       </c>
@@ -4378,7 +4378,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="91"/>
+      <c r="A14" s="92"/>
       <c r="B14" s="69" t="s">
         <v>64</v>
       </c>
@@ -4391,7 +4391,7 @@
       <c r="E14" s="72"/>
     </row>
     <row r="15" spans="1:5" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="93"/>
+      <c r="A15" s="94"/>
       <c r="B15" s="73" t="s">
         <v>66</v>
       </c>
@@ -5648,6 +5648,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="9557458c-24b5-4c97-84ed-4c402655f54f">
@@ -5656,15 +5665,6 @@
     <TaxCatchAll xmlns="72e3c584-9879-4b35-b9d8-6a248c93e240" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5687,6 +5687,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192A017-E4B6-4D7F-8544-3BE30BB952E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3314153-DE99-46E1-9177-E565F1EC3082}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5695,12 +5703,4 @@
     <ds:schemaRef ds:uri="72e3c584-9879-4b35-b9d8-6a248c93e240"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192A017-E4B6-4D7F-8544-3BE30BB952E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Scripts_Data/Data_Vehicle/sm_car_ARTTU_Powertrain.xlsx
+++ b/Scripts_Data/Data_Vehicle/sm_car_ARTTU_Powertrain.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Desktop/FSAE/Vehicle Model/VehicleModel/Scripts_Data/Data_Vehicle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2458B5-5250-044B-A5D4-803D0CC25C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE01982-3663-F043-86F0-47023825F017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7040" yWindow="720" windowWidth="17160" windowHeight="19820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3945,122 +3945,122 @@
   <sheetData>
     <row r="1" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="90">
-        <v>195.6</v>
+        <v>154.80000000000001</v>
       </c>
       <c r="B1" s="90">
-        <v>193.7</v>
+        <v>153.69999999999999</v>
       </c>
       <c r="C1" s="90">
-        <v>192.4</v>
+        <v>152.4</v>
       </c>
       <c r="D1" s="90">
-        <v>191.1</v>
+        <v>151.69999999999999</v>
       </c>
       <c r="E1" s="90">
-        <v>190.8</v>
+        <v>150.30000000000001</v>
       </c>
       <c r="F1" s="90">
-        <v>189.1</v>
+        <v>148.80000000000001</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="90">
-        <v>187</v>
+        <v>160.69999999999999</v>
       </c>
       <c r="B2" s="90">
-        <v>186.4</v>
+        <v>159.4</v>
       </c>
       <c r="C2" s="90">
-        <v>185.2</v>
+        <v>158.6</v>
       </c>
       <c r="D2" s="90">
-        <v>184.8</v>
+        <v>157.5</v>
       </c>
       <c r="E2" s="90">
-        <v>182.4</v>
+        <v>156.9</v>
       </c>
       <c r="F2" s="90">
-        <v>180.9</v>
+        <v>155.19999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="90">
-        <v>179.5</v>
+        <v>169.8</v>
       </c>
       <c r="B3" s="90">
-        <v>178.2</v>
+        <v>168.7</v>
       </c>
       <c r="C3" s="90">
-        <v>177.9</v>
+        <v>166.5</v>
       </c>
       <c r="D3" s="90">
-        <v>176.7</v>
+        <v>164.7</v>
       </c>
       <c r="E3" s="90">
-        <v>174.9</v>
+        <v>161.9</v>
       </c>
       <c r="F3" s="90">
-        <v>171.2</v>
+        <v>161.19999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="90">
-        <v>169.8</v>
+        <v>179.5</v>
       </c>
       <c r="B4" s="90">
-        <v>168.7</v>
+        <v>178.2</v>
       </c>
       <c r="C4" s="90">
-        <v>166.5</v>
+        <v>177.9</v>
       </c>
       <c r="D4" s="90">
-        <v>164.7</v>
+        <v>176.7</v>
       </c>
       <c r="E4" s="90">
-        <v>161.9</v>
+        <v>174.9</v>
       </c>
       <c r="F4" s="90">
-        <v>161.19999999999999</v>
+        <v>171.2</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A5" s="90">
-        <v>160.69999999999999</v>
+        <v>187</v>
       </c>
       <c r="B5" s="90">
-        <v>159.4</v>
+        <v>186.4</v>
       </c>
       <c r="C5" s="90">
-        <v>158.6</v>
+        <v>185.2</v>
       </c>
       <c r="D5" s="90">
-        <v>157.5</v>
+        <v>184.8</v>
       </c>
       <c r="E5" s="90">
-        <v>156.9</v>
+        <v>182.4</v>
       </c>
       <c r="F5" s="90">
-        <v>155.19999999999999</v>
+        <v>180.9</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="90">
-        <v>154.80000000000001</v>
+        <v>195.6</v>
       </c>
       <c r="B6" s="90">
-        <v>153.69999999999999</v>
+        <v>193.7</v>
       </c>
       <c r="C6" s="90">
-        <v>152.4</v>
+        <v>192.4</v>
       </c>
       <c r="D6" s="90">
-        <v>151.69999999999999</v>
+        <v>191.1</v>
       </c>
       <c r="E6" s="90">
-        <v>150.30000000000001</v>
+        <v>190.8</v>
       </c>
       <c r="F6" s="90">
-        <v>148.80000000000001</v>
+        <v>189.1</v>
       </c>
     </row>
   </sheetData>
@@ -5387,6 +5387,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009342B7EAA7728A4FA80A5CCAFE8D7EAF" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d037a5681ee6af0e7b5b5d0a2f99b20">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9557458c-24b5-4c97-84ed-4c402655f54f" xmlns:ns3="72e3c584-9879-4b35-b9d8-6a248c93e240" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="966978c8b125399653e7c255ac8e342d" ns2:_="" ns3:_="">
     <xsd:import namespace="9557458c-24b5-4c97-84ed-4c402655f54f"/>
@@ -5647,15 +5656,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5668,6 +5668,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192A017-E4B6-4D7F-8544-3BE30BB952E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A290CD9-4138-4944-8A1F-A307385BF4B2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5686,14 +5694,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192A017-E4B6-4D7F-8544-3BE30BB952E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3314153-DE99-46E1-9177-E565F1EC3082}">
   <ds:schemaRefs>

--- a/Scripts_Data/Data_Vehicle/sm_car_ARTTU_Powertrain.xlsx
+++ b/Scripts_Data/Data_Vehicle/sm_car_ARTTU_Powertrain.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Desktop/FSAE/Vehicle Model/VehicleModel/Scripts_Data/Data_Vehicle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE01982-3663-F043-86F0-47023825F017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D442043-BB6E-644C-9EC3-480B22E38459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7040" yWindow="720" windowWidth="17160" windowHeight="19820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7040" yWindow="720" windowWidth="17160" windowHeight="19820" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power" sheetId="5" r:id="rId1"/>
@@ -24,6 +24,14 @@
     <sheet name="ThermalLoss" sheetId="8" r:id="rId9"/>
     <sheet name="LossTable" sheetId="7" r:id="rId10"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">TrqSpd!$B$2:$B$48</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">TrqSpd!$C$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">TrqSpd!$C$2:$C$48</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">TrqSpd!$B$2:$B$48</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">TrqSpd!$C$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">TrqSpd!$C$2:$C$48</definedName>
+  </definedNames>
   <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1222,366 +1230,183 @@
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.14461399999999999"/>
-          <c:y val="5.5157699999999997E-2"/>
-          <c:w val="0.85038599999999998"/>
-          <c:h val="0.76626099999999997"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Series1</c:v>
+            <c:strRef>
+              <c:f>TrqSpd!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Torque [Nm]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="47625" cap="flat">
+            <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="42719B"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="diamond"/>
-            <c:size val="10"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="42719B"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln w="9525" cap="flat">
+              <a:ln w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="42719B"/>
+                  <a:schemeClr val="accent1"/>
                 </a:solidFill>
-                <a:prstDash val="solid"/>
-                <a:round/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:cat>
-            <c:strLit>
-              <c:ptCount val="49"/>
-              <c:pt idx="0">
-                <c:v>0</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>100</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>200</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>300</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>400</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>500</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>600</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>700</c:v>
-              </c:pt>
-              <c:pt idx="8">
-                <c:v>800</c:v>
-              </c:pt>
-              <c:pt idx="9">
-                <c:v>900</c:v>
-              </c:pt>
-              <c:pt idx="10">
-                <c:v>1000</c:v>
-              </c:pt>
-              <c:pt idx="11">
-                <c:v>1100</c:v>
-              </c:pt>
-              <c:pt idx="12">
-                <c:v>1200</c:v>
-              </c:pt>
-              <c:pt idx="13">
-                <c:v>1300</c:v>
-              </c:pt>
-              <c:pt idx="14">
-                <c:v>1400</c:v>
-              </c:pt>
-              <c:pt idx="15">
-                <c:v>1500</c:v>
-              </c:pt>
-              <c:pt idx="16">
-                <c:v>1600</c:v>
-              </c:pt>
-              <c:pt idx="17">
-                <c:v>1700</c:v>
-              </c:pt>
-              <c:pt idx="18">
-                <c:v>1800</c:v>
-              </c:pt>
-              <c:pt idx="19">
-                <c:v>1900</c:v>
-              </c:pt>
-              <c:pt idx="20">
-                <c:v>2000</c:v>
-              </c:pt>
-              <c:pt idx="21">
-                <c:v>2100</c:v>
-              </c:pt>
-              <c:pt idx="22">
-                <c:v>2200</c:v>
-              </c:pt>
-              <c:pt idx="23">
-                <c:v>2300</c:v>
-              </c:pt>
-              <c:pt idx="24">
-                <c:v>2400</c:v>
-              </c:pt>
-              <c:pt idx="25">
-                <c:v>2500</c:v>
-              </c:pt>
-              <c:pt idx="26">
-                <c:v>2600</c:v>
-              </c:pt>
-              <c:pt idx="27">
-                <c:v>2700</c:v>
-              </c:pt>
-              <c:pt idx="28">
-                <c:v>2800</c:v>
-              </c:pt>
-              <c:pt idx="29">
-                <c:v>2900</c:v>
-              </c:pt>
-              <c:pt idx="30">
-                <c:v>3000</c:v>
-              </c:pt>
-              <c:pt idx="31">
-                <c:v>3100</c:v>
-              </c:pt>
-              <c:pt idx="32">
-                <c:v>3200</c:v>
-              </c:pt>
-              <c:pt idx="33">
-                <c:v>3300</c:v>
-              </c:pt>
-              <c:pt idx="34">
-                <c:v>3400</c:v>
-              </c:pt>
-              <c:pt idx="35">
-                <c:v>3500</c:v>
-              </c:pt>
-              <c:pt idx="36">
-                <c:v>3600</c:v>
-              </c:pt>
-              <c:pt idx="37">
-                <c:v>3700</c:v>
-              </c:pt>
-              <c:pt idx="38">
-                <c:v>3800</c:v>
-              </c:pt>
-              <c:pt idx="39">
-                <c:v>3900</c:v>
-              </c:pt>
-              <c:pt idx="40">
-                <c:v>4000</c:v>
-              </c:pt>
-              <c:pt idx="41">
-                <c:v>4100</c:v>
-              </c:pt>
-              <c:pt idx="42">
-                <c:v>4200</c:v>
-              </c:pt>
-              <c:pt idx="43">
-                <c:v>4300</c:v>
-              </c:pt>
-              <c:pt idx="44">
-                <c:v>4400</c:v>
-              </c:pt>
-              <c:pt idx="45">
-                <c:v>4500</c:v>
-              </c:pt>
-              <c:pt idx="46">
-                <c:v>4600</c:v>
-              </c:pt>
-              <c:pt idx="47">
-                <c:v>Engine Speed [rpm]</c:v>
-              </c:pt>
-            </c:strLit>
-          </c:cat>
-          <c:val>
+          <c:xVal>
             <c:numRef>
-              <c:f>(TrqSpd!$C$1:$C$48,TrqSpd!$B$1)</c:f>
+              <c:f>TrqSpd!$B$2:$B$48</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="47"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3700</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3800</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4200</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4400</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4600</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>TrqSpd!$C$2:$C$48</c:f>
               <c:numCache>
                 <c:formatCode>0.0000000000000</c:formatCode>
-                <c:ptCount val="49"/>
-                <c:pt idx="0" formatCode="@">
-                  <c:v>0</c:v>
+                <c:ptCount val="47"/>
+                <c:pt idx="0">
+                  <c:v>51.0306904761905</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>51.0306904761905</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>51.0306904761905</c:v>
+                <c:pt idx="2" formatCode="0.000000000000">
+                  <c:v>44.843689833269003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51.0306904761905</c:v>
+                  <c:v>36.821568821896101</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>51.0306904761905</c:v>
+                <c:pt idx="4" formatCode="0.000000000000">
+                  <c:v>30.062728824122001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>51.0306904761905</c:v>
+                  <c:v>25.337074314098199</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>51.0306904761905</c:v>
+                  <c:v>21.037412309536101</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51.0306904761905</c:v>
+                  <c:v>17.084032426778201</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>51.0306904761905</c:v>
-                </c:pt>
-                <c:pt idx="38" formatCode="0.000000000000">
-                  <c:v>44.843689833269003</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>36.821568821896101</c:v>
-                </c:pt>
-                <c:pt idx="40" formatCode="0.000000000000">
-                  <c:v>30.062728824122001</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>25.337074314098199</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>21.037412309536101</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>17.084032426778201</c:v>
-                </c:pt>
-                <c:pt idx="44">
                   <c:v>13.4184887499186</c:v>
                 </c:pt>
-                <c:pt idx="45" formatCode="0.00000000000000">
+                <c:pt idx="9" formatCode="0.00000000000000">
                   <c:v>9.9959268483305195</c:v>
                 </c:pt>
-                <c:pt idx="46" formatCode="0.00000000000000">
+                <c:pt idx="10" formatCode="0.00000000000000">
                   <c:v>6.7769653459149204</c:v>
                 </c:pt>
-                <c:pt idx="47" formatCode="0.00000000000000">
+                <c:pt idx="11" formatCode="0.00000000000000">
                   <c:v>3.7395748460445501</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="@">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
+          </c:yVal>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DF2F-4F66-8541-29E2A3834BE7}"/>
+              <c16:uniqueId val="{00000000-4BFF-AF40-851F-358193BC1C04}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1593,13 +1418,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="2094734552"/>
-        <c:axId val="2094734553"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="2094734552"/>
+        <c:axId val="1335347840"/>
+        <c:axId val="1335360832"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1335347840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1607,79 +1430,61 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="6350" cap="flat">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:miter lim="400000"/>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Helvetica Neue"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Helvetica Neue"/>
-                  </a:rPr>
-                  <a:t>Engine Speed [rpm]</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
+        <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="12700" cap="flat">
-            <a:noFill/>
-            <a:prstDash val="solid"/>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
             <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="0"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Helvetica Neue"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2094734553"/>
+        <c:crossAx val="1335360832"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:tickLblSkip val="5"/>
-        <c:noMultiLvlLbl val="1"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
-        <c:axId val="2094734553"/>
+        <c:axId val="1335360832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1687,105 +1492,103 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="12700" cap="flat">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="888888"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Helvetica Neue"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Helvetica Neue"/>
-                  </a:rPr>
-                  <a:t>Torque [Nm]</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
-        <c:numFmt formatCode="@" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:numFmt formatCode="0.0000000000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="888888"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
-            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="0"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Helvetica Neue"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2094734552"/>
+        <c:crossAx val="1335347840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="15"/>
-        <c:minorUnit val="7.5"/>
       </c:valAx>
       <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
-          <a:miter lim="400000"/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="12700" cap="flat">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:srgbClr val="888888"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:prstDash val="solid"/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -1794,27 +1597,583 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>6349</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>273050</xdr:colOff>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>249084</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>148828</xdr:rowOff>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="2D Line Chart">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CD44857-1E7D-75DF-9518-07966F2710B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4434,7 +4793,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.1640625" style="1" customWidth="1"/>
@@ -4464,415 +4823,100 @@
     </row>
     <row r="3" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="33"/>
-      <c r="B3" s="36">
-        <v>100</v>
-      </c>
-      <c r="C3" s="37">
+      <c r="B3" s="34">
+        <v>3600</v>
+      </c>
+      <c r="C3" s="35">
         <v>51.0306904761905</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="33"/>
-      <c r="B4" s="34">
-        <v>200</v>
-      </c>
-      <c r="C4" s="35">
-        <v>51.0306904761905</v>
+      <c r="B4" s="36">
+        <v>3700</v>
+      </c>
+      <c r="C4" s="38">
+        <v>44.843689833269003</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="33"/>
-      <c r="B5" s="36">
-        <v>300</v>
-      </c>
-      <c r="C5" s="37">
-        <v>51.0306904761905</v>
+      <c r="B5" s="34">
+        <v>3800</v>
+      </c>
+      <c r="C5" s="35">
+        <v>36.821568821896101</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="33"/>
-      <c r="B6" s="34">
-        <v>400</v>
-      </c>
-      <c r="C6" s="35">
-        <v>51.0306904761905</v>
+      <c r="B6" s="36">
+        <v>3900</v>
+      </c>
+      <c r="C6" s="38">
+        <v>30.062728824122001</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="33"/>
-      <c r="B7" s="36">
-        <v>500</v>
-      </c>
-      <c r="C7" s="37">
-        <v>51.0306904761905</v>
+      <c r="B7" s="34">
+        <v>4000</v>
+      </c>
+      <c r="C7" s="35">
+        <v>25.337074314098199</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="33"/>
-      <c r="B8" s="34">
-        <v>600</v>
-      </c>
-      <c r="C8" s="35">
-        <v>51.0306904761905</v>
+      <c r="B8" s="36">
+        <v>4100</v>
+      </c>
+      <c r="C8" s="37">
+        <v>21.037412309536101</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="33"/>
-      <c r="B9" s="36">
-        <v>700</v>
-      </c>
-      <c r="C9" s="37">
-        <v>51.0306904761905</v>
+      <c r="B9" s="34">
+        <v>4200</v>
+      </c>
+      <c r="C9" s="35">
+        <v>17.084032426778201</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="33"/>
-      <c r="B10" s="34">
-        <v>800</v>
-      </c>
-      <c r="C10" s="35">
-        <v>51.0306904761905</v>
+      <c r="B10" s="36">
+        <v>4300</v>
+      </c>
+      <c r="C10" s="37">
+        <v>13.4184887499186</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="33"/>
-      <c r="B11" s="36">
-        <v>900</v>
-      </c>
-      <c r="C11" s="37">
-        <v>51.0306904761905</v>
+      <c r="B11" s="34">
+        <v>4400</v>
+      </c>
+      <c r="C11" s="39">
+        <v>9.9959268483305195</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="33"/>
-      <c r="B12" s="34">
-        <v>1000</v>
-      </c>
-      <c r="C12" s="35">
-        <v>51.0306904761905</v>
+      <c r="B12" s="36">
+        <v>4500</v>
+      </c>
+      <c r="C12" s="40">
+        <v>6.7769653459149204</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="33"/>
-      <c r="B13" s="36">
-        <v>1100</v>
-      </c>
-      <c r="C13" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="33"/>
-      <c r="B14" s="34">
-        <v>1200</v>
-      </c>
-      <c r="C14" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="33"/>
-      <c r="B15" s="36">
-        <v>1300</v>
-      </c>
-      <c r="C15" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="33"/>
-      <c r="B16" s="34">
-        <v>1400</v>
-      </c>
-      <c r="C16" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
-      <c r="B17" s="36">
-        <v>1500</v>
-      </c>
-      <c r="C17" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="33"/>
-      <c r="B18" s="34">
-        <v>1600</v>
-      </c>
-      <c r="C18" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="33"/>
-      <c r="B19" s="36">
-        <v>1700</v>
-      </c>
-      <c r="C19" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="33"/>
-      <c r="B20" s="34">
-        <v>1800</v>
-      </c>
-      <c r="C20" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="33"/>
-      <c r="B21" s="36">
-        <v>1900</v>
-      </c>
-      <c r="C21" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="33"/>
-      <c r="B22" s="34">
-        <v>2000</v>
-      </c>
-      <c r="C22" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="33"/>
-      <c r="B23" s="36">
-        <v>2100</v>
-      </c>
-      <c r="C23" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="33"/>
-      <c r="B24" s="34">
-        <v>2200</v>
-      </c>
-      <c r="C24" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="33"/>
-      <c r="B25" s="36">
-        <v>2300</v>
-      </c>
-      <c r="C25" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="33"/>
-      <c r="B26" s="34">
-        <v>2400</v>
-      </c>
-      <c r="C26" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="33"/>
-      <c r="B27" s="36">
-        <v>2500</v>
-      </c>
-      <c r="C27" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="33"/>
-      <c r="B28" s="34">
-        <v>2600</v>
-      </c>
-      <c r="C28" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="33"/>
-      <c r="B29" s="36">
-        <v>2700</v>
-      </c>
-      <c r="C29" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="33"/>
-      <c r="B30" s="34">
-        <v>2800</v>
-      </c>
-      <c r="C30" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="33"/>
-      <c r="B31" s="36">
-        <v>2900</v>
-      </c>
-      <c r="C31" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="33"/>
-      <c r="B32" s="34">
-        <v>3000</v>
-      </c>
-      <c r="C32" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="33"/>
-      <c r="B33" s="36">
-        <v>3100</v>
-      </c>
-      <c r="C33" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="33"/>
-      <c r="B34" s="34">
-        <v>3200</v>
-      </c>
-      <c r="C34" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="33"/>
-      <c r="B35" s="36">
-        <v>3300</v>
-      </c>
-      <c r="C35" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="33"/>
-      <c r="B36" s="34">
-        <v>3400</v>
-      </c>
-      <c r="C36" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="33"/>
-      <c r="B37" s="36">
-        <v>3500</v>
-      </c>
-      <c r="C37" s="37">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="33"/>
-      <c r="B38" s="34">
-        <v>3600</v>
-      </c>
-      <c r="C38" s="35">
-        <v>51.0306904761905</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="33"/>
-      <c r="B39" s="36">
-        <v>3700</v>
-      </c>
-      <c r="C39" s="38">
-        <v>44.843689833269003</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="33"/>
-      <c r="B40" s="34">
-        <v>3800</v>
-      </c>
-      <c r="C40" s="35">
-        <v>36.821568821896101</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="33"/>
-      <c r="B41" s="36">
-        <v>3900</v>
-      </c>
-      <c r="C41" s="38">
-        <v>30.062728824122001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="33"/>
-      <c r="B42" s="34">
-        <v>4000</v>
-      </c>
-      <c r="C42" s="35">
-        <v>25.337074314098199</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="33"/>
-      <c r="B43" s="36">
-        <v>4100</v>
-      </c>
-      <c r="C43" s="37">
-        <v>21.037412309536101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="33"/>
-      <c r="B44" s="34">
-        <v>4200</v>
-      </c>
-      <c r="C44" s="35">
-        <v>17.084032426778201</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="33"/>
-      <c r="B45" s="36">
-        <v>4300</v>
-      </c>
-      <c r="C45" s="37">
-        <v>13.4184887499186</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="33"/>
-      <c r="B46" s="34">
-        <v>4400</v>
-      </c>
-      <c r="C46" s="39">
-        <v>9.9959268483305195</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="33"/>
-      <c r="B47" s="36">
-        <v>4500</v>
-      </c>
-      <c r="C47" s="40">
-        <v>6.7769653459149204</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="41"/>
-      <c r="B48" s="34">
+      <c r="A13" s="41"/>
+      <c r="B13" s="34">
         <v>4600</v>
       </c>
-      <c r="C48" s="39">
+      <c r="C13" s="39">
         <v>3.7395748460445501</v>
       </c>
     </row>
@@ -5387,15 +5431,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009342B7EAA7728A4FA80A5CCAFE8D7EAF" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d037a5681ee6af0e7b5b5d0a2f99b20">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9557458c-24b5-4c97-84ed-4c402655f54f" xmlns:ns3="72e3c584-9879-4b35-b9d8-6a248c93e240" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="966978c8b125399653e7c255ac8e342d" ns2:_="" ns3:_="">
     <xsd:import namespace="9557458c-24b5-4c97-84ed-4c402655f54f"/>
@@ -5656,6 +5691,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5668,14 +5712,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192A017-E4B6-4D7F-8544-3BE30BB952E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A290CD9-4138-4944-8A1F-A307385BF4B2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5694,6 +5730,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192A017-E4B6-4D7F-8544-3BE30BB952E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3314153-DE99-46E1-9177-E565F1EC3082}">
   <ds:schemaRefs>

--- a/Scripts_Data/Data_Vehicle/sm_car_ARTTU_Powertrain.xlsx
+++ b/Scripts_Data/Data_Vehicle/sm_car_ARTTU_Powertrain.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Desktop/FSAE/Vehicle Model/VehicleModel/Scripts_Data/Data_Vehicle/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Desktop/FSAE/Vehicle Model/Vehicle_Model/Scripts_Data/Data_Vehicle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D442043-BB6E-644C-9EC3-480B22E38459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF700FD-AECF-AC4F-9A2F-56769913485F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7040" yWindow="720" windowWidth="17160" windowHeight="19820" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23360" yWindow="2940" windowWidth="17160" windowHeight="19820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power" sheetId="5" r:id="rId1"/>
@@ -24,14 +24,6 @@
     <sheet name="ThermalLoss" sheetId="8" r:id="rId9"/>
     <sheet name="LossTable" sheetId="7" r:id="rId10"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">TrqSpd!$B$2:$B$48</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">TrqSpd!$C$1</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">TrqSpd!$C$2:$C$48</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">TrqSpd!$B$2:$B$48</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">TrqSpd!$C$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">TrqSpd!$C$2:$C$48</definedName>
-  </definedNames>
   <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -5431,6 +5423,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009342B7EAA7728A4FA80A5CCAFE8D7EAF" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d037a5681ee6af0e7b5b5d0a2f99b20">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9557458c-24b5-4c97-84ed-4c402655f54f" xmlns:ns3="72e3c584-9879-4b35-b9d8-6a248c93e240" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="966978c8b125399653e7c255ac8e342d" ns2:_="" ns3:_="">
     <xsd:import namespace="9557458c-24b5-4c97-84ed-4c402655f54f"/>
@@ -5691,15 +5692,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5712,6 +5704,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192A017-E4B6-4D7F-8544-3BE30BB952E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A290CD9-4138-4944-8A1F-A307385BF4B2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5730,14 +5730,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8192A017-E4B6-4D7F-8544-3BE30BB952E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3314153-DE99-46E1-9177-E565F1EC3082}">
   <ds:schemaRefs>
